--- a/results/ntnu_datasets_fused.xlsx
+++ b/results/ntnu_datasets_fused.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,12 +485,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.97]</t>
+          <t>0.97 [0.96, 0.98]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.87]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -500,159 +500,169 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.85]</t>
+          <t>0.82 [0.78, 0.86]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.88 [0.81, 0.96]</t>
+          <t>0.88 [0.79, 0.98]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.96 [0.96, 0.97]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.89 [0.87, 0.91]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.88 [0.87, 0.90]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.76 [0.72, 0.81]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.94]</t>
+          <t>0.85 [0.83, 0.88]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.97 [0.97, 0.98]</t>
+          <t>0.96 [0.96, 0.97]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.89 [0.87, 0.91]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.89 [0.88, 0.91]</t>
+          <t>0.88 [0.86, 0.90]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.90 [0.88, 0.92]</t>
+          <t>0.76 [0.71, 0.82]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.93 [0.85, 1.00]</t>
+          <t>0.90 [0.84, 0.95]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>689.48 ± 350.15</t>
+          <t>0.97 [0.96, 0.98]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>879.63 ± 485.48</t>
+          <t>0.82 [0.79, 0.86]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1055.65 ± 478.74</t>
+          <t>0.89 [0.87, 0.91]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>359.98 ± 297.86</t>
+          <t>0.90 [0.87, 0.93]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>119.00 ± 122.27</t>
+          <t>0.93 [0.83, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>31716</v>
-      </c>
-      <c r="C7" t="n">
-        <v>40463</v>
-      </c>
-      <c r="D7" t="n">
-        <v>48560</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16559</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2618</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>689.48 ± 350.15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>879.63 ± 485.48</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1055.65 ± 478.74</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>359.98 ± 297.86</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>119.00 ± 122.27</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>31716</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>40463</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>48560</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>16559</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -668,6 +678,28 @@
         <v>46</v>
       </c>
       <c r="F9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F10" t="n">
         <v>46</v>
       </c>
     </row>
@@ -682,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,27 +752,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.92 [0.89, 0.95]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.92 [0.89, 0.95]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92 [0.89, 0.95]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.92 [0.89, 0.95]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.92 [0.89, 0.95]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
     </row>
@@ -752,178 +784,188 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.95 [0.91, 0.98]</t>
+          <t>0.95 [0.91, 0.99]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.87]</t>
+          <t>0.82 [0.77, 0.87]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.85 [0.80, 0.89]</t>
+          <t>0.85 [0.79, 0.90]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.93 [0.91, 0.96]</t>
+          <t>0.93 [0.90, 0.97]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.89 [0.84, 0.94]</t>
+          <t>0.89 [0.83, 0.95]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.96 [0.92, 0.99]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.80 [0.75, 0.85]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.86 [0.81, 0.91]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.90 [0.86, 0.95]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.96 [0.93, 0.98]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.96 [0.92, 0.99]</t>
+          <t>0.96 [0.91, 1.00]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.87 [0.84, 0.90]</t>
+          <t>0.80 [0.74, 0.86]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.86 [0.83, 0.89]</t>
+          <t>0.86 [0.80, 0.92]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.98]</t>
+          <t>0.90 [0.85, 0.95]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.85 [0.78, 0.92]</t>
+          <t>0.96 [0.93, 0.99]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2595.87 ± 2162.18</t>
+          <t>0.96 [0.92, 1.00]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1026.52 ± 768.00</t>
+          <t>0.87 [0.84, 0.90]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1231.81 ± 783.49</t>
+          <t>0.86 [0.82, 0.90]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>345.75 ± 571.00</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>650.47 ± 856.37</t>
+          <t>0.85 [0.77, 0.93]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>77876</v>
-      </c>
-      <c r="C7" t="n">
-        <v>31822</v>
-      </c>
-      <c r="D7" t="n">
-        <v>38186</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6915</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12359</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2595.87 ± 2162.18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1026.52 ± 768.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1231.81 ± 783.49</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>345.75 ± 571.00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>650.47 ± 856.37</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>77876</v>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>31822</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>38186</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>6915</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>12359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
         <v>31</v>
@@ -932,9 +974,31 @@
         <v>31</v>
       </c>
       <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>31</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="n">
         <v>31</v>
       </c>
     </row>
@@ -949,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,17 +1083,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 0.99]</t>
+          <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.84 [0.82, 0.86]</t>
+          <t>0.84 [0.81, 0.87]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91 [0.90, 0.93]</t>
+          <t>0.91 [0.89, 0.94]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1038,46 +1102,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.00 [1.00, 1.00]</t>
+          <t>0.88 [0.85, 0.90]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.81]</t>
+          <t>0.88 [0.85, 0.90]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96 [0.95, 0.97]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>0.88 [0.85, 0.90]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.88 [0.85, 0.90]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.88 [0.85, 0.90]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 0.99]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.93 [0.92, 0.94]</t>
+          <t>0.77 [0.73, 0.82]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.87 [0.84, 0.90]</t>
+          <t>0.96 [0.95, 0.97]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1086,22 +1158,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>768.06 ± 211.32</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>539.78 ± 177.87</t>
+          <t>0.93 [0.91, 0.94]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1214.89 ± 237.88</t>
+          <t>0.87 [0.84, 0.91]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1110,17 +1182,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>13825</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9716</v>
-      </c>
-      <c r="D7" t="n">
-        <v>21868</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>768.06 ± 211.32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>539.78 ± 177.87</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1214.89 ± 237.88</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1128,17 +1206,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>13825</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>9716</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>21868</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1146,7 +1224,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1160,6 +1238,24 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/ntnu_datasets_fused.xlsx
+++ b/results/ntnu_datasets_fused.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Children" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Adults" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Older Adults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Children matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Adults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adults matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Older Adults" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Older Adults matrix" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -714,292 +717,879 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sedentary</t>
+          <t>pred</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>n_total</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.92 [0.88, 0.96]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.92 [0.88, 0.96]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.92 [0.88, 0.96]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.92 [0.88, 0.96]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.92 [0.88, 0.96]</t>
-        </is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.42911911201934</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9285963232736065</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2124498520473197</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8344013358244373</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fscore</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.95 [0.91, 0.99]</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.82 [0.77, 0.87]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.85 [0.79, 0.90]</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.93 [0.90, 0.97]</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.89 [0.83, 0.95]</t>
-        </is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kappa</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5536541889483065</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0251660994976503</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05666040043598509</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.428530714778792e-05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0502879136881528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.96 [0.91, 1.00]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.80 [0.74, 0.86]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.86 [0.80, 0.92]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.90 [0.85, 0.95]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.96 [0.93, 0.99]</t>
-        </is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6672266990323485</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03032848631965221</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.09482915749717372</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07237337933408468</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.96 [0.92, 1.00]</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.87 [0.84, 0.90]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.86 [0.82, 0.90]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.97 [0.96, 0.99]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.85 [0.77, 0.93]</t>
-        </is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01590909090909091</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.07462025072446365</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04899385662066762</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2595.87 ± 2162.18</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1026.52 ± 768.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1231.81 ± 783.49</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>345.75 ± 571.00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>650.47 ± 856.37</t>
-        </is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>46</v>
+      </c>
+      <c r="D7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>77876</v>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>31822</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>38186</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>6915</v>
+        <v>41.44945517513595</v>
       </c>
       <c r="F8" t="n">
-        <v>12359</v>
+        <v>0.9010751125029554</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.09095915432766315</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8740635779068955</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9280866470990152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>30</v>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>0.1966494363978454</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>0.004274987747779248</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01104627273111248</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0009946496637298786</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.007555325831828618</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n_total</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>31</v>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>2.745028827657298</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>0.0596745397316804</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.06245148622318733</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.04112873757287619</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0782203418904846</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.608866560808907</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03497536001758494</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.04421252057527844</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02184586208056489</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.04810485795460499</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>46</v>
+      </c>
+      <c r="D12" t="n">
+        <v>46</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2702844814572073</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005875749596895812</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01110099107243046</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.002579162171254885</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.009172337022536739</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>46</v>
+      </c>
+      <c r="D13" t="n">
+        <v>46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.03929353700739565</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0008542073262477315</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00326490405117163</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.001823764149669269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>46</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44.72528960992032</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9722889045634853</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.02724622359283835</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9641977749061144</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9803800342208562</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7066240181898803</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01536139169978001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01721812425429154</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0102482399514836</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.02047454344807641</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>46</v>
+      </c>
+      <c r="D16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2585083534251972</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.005619746813591243</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.006248202598267305</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.003764259678801999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.007475233948380487</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>46</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01442449060383473</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0003135758826920593</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0009270494148104216</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.827618882943631e-05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0005888755765546823</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.301298303259578</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.02828909354912125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.02989838451400913</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01941036931695406</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.03716781778128844</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>46</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.613210563200169</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01333066441739498</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01447957796181161</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.009030760532593014</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01763056830219694</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>46</v>
+      </c>
+      <c r="D20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.90095593049611</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8239338245760024</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.107625446398909</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7919730121618045</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8558946369902003</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D21" t="n">
+        <v>46</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.155963289830835</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.133825288909366</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.08782925466749487</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1077432197813807</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1599073580373512</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>46</v>
+      </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.588540163102293</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03453348180657159</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0393677556759988</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02284270145277856</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.04622426216036463</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>46</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6848522112397283</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.01488809154868975</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.01456231237949837</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01056361857458446</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.01921256452279503</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>46</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.738339798608961</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.05952912605671654</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.04072834663969834</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04743430006113283</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.07162395205230024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>46</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>40.98826782704902</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8910493005880222</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05884277933761066</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8735751520918681</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9085234490841764</v>
       </c>
     </row>
   </sheetData>
@@ -1051,27 +1641,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.92 [0.91, 0.94]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.92 [0.91, 0.94]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92 [0.91, 0.94]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.92 [0.91, 0.94]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.92 [0.91, 0.94]</t>
+          <t>0.92 [0.88, 0.96]</t>
         </is>
       </c>
     </row>
@@ -1083,6 +1673,1191 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.95 [0.91, 0.99]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.82 [0.77, 0.87]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.85 [0.79, 0.90]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.93 [0.90, 0.97]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.89 [0.83, 0.95]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.96 [0.91, 1.00]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.80 [0.74, 0.86]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.86 [0.80, 0.92]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.90 [0.85, 0.95]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.96 [0.93, 0.99]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.96 [0.92, 1.00]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.87 [0.84, 0.90]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.86 [0.82, 0.90]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.97 [0.96, 0.99]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.85 [0.77, 0.93]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2595.87 ± 2162.18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1026.52 ± 768.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1231.81 ± 783.49</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>345.75 ± 571.00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>650.47 ± 856.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>support_total</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>77876</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31822</v>
+      </c>
+      <c r="D8" t="n">
+        <v>38186</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6915</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.20128091496537</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8526989955244934</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1707353007931282</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7704072147033262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9349907763456605</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.05800883215332904</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.003053096429122581</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.009180714226198402</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.007478059043031524</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2845162899829668</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01497454157805088</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03138451094449853</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03010139164260498</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.058052363054638</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05568696647655989</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07346164110244652</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02027958885586174</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09109434409725803</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.398141599843694</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07358639999177335</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1191580423531833</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01615406198752757</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1310187379960192</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19.41652497158246</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9708262485791229</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.03329226488113525</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9552449889924036</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9864075081658422</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.23968618970183</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0119843094850915</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01965816229488478</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.002784006327344556</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02118461264283845</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3437888387157137</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01718944193578568</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0217172268610419</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.007025466897328424</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02735341697424295</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3813447667611085</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.01271149222537028</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05437573423613015</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.03301572507986879</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>31</v>
+      </c>
+      <c r="E14" t="n">
+        <v>28.78506758122903</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9595022527076343</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1136303358561093</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9170719879770791</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8051030837922817</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02683676945974272</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.06925665606917346</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0009759090721682476</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0526976298473172</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0284845682175833</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0009494856072527767</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.002527648112145168</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.646290612745233e-06</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.001893324923892808</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" t="n">
+        <v>31</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.08105844160168013</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.002614788438763875</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.009626346805485389</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.006145760953853126</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0719494670256695</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.002320950549215145</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.004836241923342058</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0005470026900010572</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.004094898408429233</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5474176694178522</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01765863449735007</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.04533005705349152</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.001031435332647268</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.03428583366205287</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>31</v>
+      </c>
+      <c r="D20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26.92058848959772</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8684060803096038</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.08984388750384137</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8354510763153509</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9013610843038566</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.378985932357089</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1089995462050674</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.07723650935553122</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.08066896585028416</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1373301265598506</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>31</v>
+      </c>
+      <c r="D22" t="n">
+        <v>31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1860890739075099</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.006002873351855157</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.02292297095886271</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01441108698216099</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>31</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3102449392239586</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.01000790126528899</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01765036532339331</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.003533694996024655</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01648210753455332</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>31</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.09974363454875398</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.003217536598346903</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.003813619228905689</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.001818689771780398</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004616383424913407</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>31</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.698960904275673</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1193213194927636</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0914289850870221</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0857848970109952</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1528577419745321</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>31</v>
+      </c>
+      <c r="D26" t="n">
+        <v>31</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26.7049614480441</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8614503692917451</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1070677754544151</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8221775921915204</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9007231463919698</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.92 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.92 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.92 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.92 [0.91, 0.94]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.92 [0.91, 0.94]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fscore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>0.99 [0.99, 1.00]</t>
         </is>
       </c>
@@ -1218,8 +2993,12 @@
       <c r="D8" t="n">
         <v>21868</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1236,8 +3015,12 @@
       <c r="D9" t="n">
         <v>18</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1254,8 +3037,568 @@
       <c r="D10" t="n">
         <v>18</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.7944229019026</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9885790501057</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00562420247540081</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9857822000138422</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9913759001975578</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.19458729536756</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01081040529819778</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005564969150885503</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00804301124563375</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01357779935076181</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01098980272984041</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0006105445961022451</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0007541258121268074</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0002355266524659061</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0009855625397385843</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01528662420382166</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0008492569002123143</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.003603091878657567</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.002641032337862689</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002178649237472767</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0001210360687484871</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0005135125498812981</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0003763998520737491</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.71323124041138</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9285128466895211</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03029159081961753</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9134491929649404</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9435765004141017</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.269303486147326</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.07051686034151811</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.02966164100476489</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.05576647328990001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.08526724739313621</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1511520737327189</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.008397337429595494</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.03562688544227151</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02611417075087884</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.002349256068911512</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0001305142260506395</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.000553724965690327</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0004058751733011375</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.008403365539335019</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0004668536410741677</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0007940374120269187</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.198812574476583e-05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0008617191564035695</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.111215790220839</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1172897661233799</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0679451680833392</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08350142894555809</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1510781033012017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.7268795144382</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8737155285798998</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.07279049234503902</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8375176683335739</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9099133888262256</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/ntnu_datasets_fused.xlsx
+++ b/results/ntnu_datasets_fused.xlsx
@@ -498,12 +498,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.89 [0.87, 0.90]</t>
+          <t>0.89 [0.87, 0.91]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.86]</t>
+          <t>0.83 [0.79, 0.87]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -520,27 +520,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.88]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.88]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.88]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.88]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.85 [0.83, 0.88]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.76 [0.71, 0.82]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.89 [0.87, 0.91]</t>
+          <t>0.90 [0.88, 0.92]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.90 [0.87, 0.93]</t>
+          <t>0.90 [0.87, 0.92]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -884,19 +884,19 @@
         <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6672266990323485</v>
+        <v>0.6172266990323487</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03032848631965221</v>
+        <v>0.02805575904692494</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09482915749717372</v>
+        <v>0.0843075897878116</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07237337933408468</v>
+        <v>0.06543565027962775</v>
       </c>
     </row>
     <row r="6">
@@ -917,19 +917,19 @@
         <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01590909090909091</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07462025072446365</v>
+        <v>0.0852802865422442</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04899385662066762</v>
+        <v>0.05599297899504874</v>
       </c>
     </row>
     <row r="7">
@@ -983,19 +983,19 @@
         <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>41.44945517513595</v>
+        <v>41.25929153923031</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9010751125029554</v>
+        <v>0.8969411204180503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09095915432766315</v>
+        <v>0.08982734462742603</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8740635779068955</v>
+        <v>0.8702656918148406</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9280866470990152</v>
+        <v>0.92361654902126</v>
       </c>
     </row>
     <row r="9">
@@ -1049,19 +1049,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>2.745028827657298</v>
+        <v>2.704688190352528</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0596745397316804</v>
+        <v>0.05879756935548974</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06245148622318733</v>
+        <v>0.06181799045329558</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04112873757287619</v>
+        <v>0.0404398922186404</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0782203418904846</v>
+        <v>0.07715524649233907</v>
       </c>
     </row>
     <row r="11">
@@ -1082,19 +1082,19 @@
         <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>1.608866560808907</v>
+        <v>1.839370834019313</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03497536001758494</v>
+        <v>0.03998632247868071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04421252057527844</v>
+        <v>0.0448943205547819</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02184586208056489</v>
+        <v>0.02665435494011172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04810485795460499</v>
+        <v>0.05331829001724971</v>
       </c>
     </row>
     <row r="12">
@@ -1214,19 +1214,19 @@
         <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7066240181898803</v>
+        <v>0.7020679421297675</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01536139169978001</v>
+        <v>0.01526234656803842</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01721812425429154</v>
+        <v>0.01728883029447463</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0102482399514836</v>
+        <v>0.01012819771763973</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02047454344807641</v>
+        <v>0.02039649541843712</v>
       </c>
     </row>
     <row r="16">
@@ -1247,19 +1247,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2585083534251972</v>
+        <v>0.2630644294853099</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005619746813591243</v>
+        <v>0.005718791945332824</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006248202598267305</v>
+        <v>0.00623039252991519</v>
       </c>
       <c r="H16" t="n">
-        <v>0.003764259678801999</v>
+        <v>0.003868593747990363</v>
       </c>
       <c r="I16" t="n">
-        <v>0.007475233948380487</v>
+        <v>0.007568990142675285</v>
       </c>
     </row>
     <row r="17">
@@ -1313,19 +1313,19 @@
         <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>1.301298303259578</v>
+        <v>1.262689562366758</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02828909354912125</v>
+        <v>0.02744977309492953</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02989838451400913</v>
+        <v>0.02976317053830255</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01941036931695406</v>
+        <v>0.0186112024570835</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03716781778128844</v>
+        <v>0.03628834373277556</v>
       </c>
     </row>
     <row r="19">
@@ -1346,19 +1346,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.613210563200169</v>
+        <v>0.6145655767503047</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01333066441739498</v>
+        <v>0.01336012123370228</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01447957796181161</v>
+        <v>0.01447013816566209</v>
       </c>
       <c r="H19" t="n">
-        <v>0.009030760532593014</v>
+        <v>0.009063020622327349</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01763056830219694</v>
+        <v>0.0176572218450772</v>
       </c>
     </row>
     <row r="20">
@@ -1379,19 +1379,19 @@
         <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>37.90095593049611</v>
+        <v>37.87258370827457</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8239338245760024</v>
+        <v>0.8233170371364037</v>
       </c>
       <c r="G20" t="n">
-        <v>0.107625446398909</v>
+        <v>0.1067402100709649</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7919730121618045</v>
+        <v>0.7916191074619883</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8558946369902003</v>
+        <v>0.8550149668108191</v>
       </c>
     </row>
     <row r="21">
@@ -1412,19 +1412,19 @@
         <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>6.155963289830835</v>
+        <v>6.221589239395054</v>
       </c>
       <c r="F21" t="n">
-        <v>0.133825288909366</v>
+        <v>0.135251939986849</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08782925466749487</v>
+        <v>0.08764976306591665</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1077432197813807</v>
+        <v>0.1092231732850084</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1599073580373512</v>
+        <v>0.1612807066886896</v>
       </c>
     </row>
     <row r="22">
@@ -1478,19 +1478,19 @@
         <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>1.588540163102293</v>
+        <v>1.302008196534424</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03453348180657159</v>
+        <v>0.02830452601161791</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0393677556759988</v>
+        <v>0.03747023401118309</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02284270145277856</v>
+        <v>0.01717724003587622</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04622426216036463</v>
+        <v>0.03943181198735961</v>
       </c>
     </row>
     <row r="24">
@@ -1511,19 +1511,19 @@
         <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6848522112397283</v>
+        <v>0.6816549870795053</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01488809154868975</v>
+        <v>0.01481858667564142</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01456231237949837</v>
+        <v>0.01453432475617453</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01056361857458446</v>
+        <v>0.01050242499973654</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01921256452279503</v>
+        <v>0.01913474835154631</v>
       </c>
     </row>
     <row r="25">
@@ -1544,19 +1544,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>2.738339798608961</v>
+        <v>2.624810777430837</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05952912605671654</v>
+        <v>0.0570611038571921</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04072834663969834</v>
+        <v>0.04039828527772626</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04743430006113283</v>
+        <v>0.04506429398723789</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07162395205230024</v>
+        <v>0.06905791372714633</v>
       </c>
     </row>
     <row r="26">
@@ -1577,19 +1577,19 @@
         <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>40.98826782704902</v>
+        <v>41.39152603895523</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8910493005880222</v>
+        <v>0.8998157834555485</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05884277933761066</v>
+        <v>0.05858913703287984</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8735751520918681</v>
+        <v>0.8824169574262741</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9085234490841764</v>
+        <v>0.9172146094848228</v>
       </c>
     </row>
   </sheetData>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82 [0.77, 0.87]</t>
+          <t>0.83 [0.78, 0.88]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.93 [0.90, 0.97]</t>
+          <t>0.93 [0.89, 0.97]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.95]</t>
+          <t>0.91 [0.86, 0.96]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.87 [0.83, 0.90]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.99]</t>
+          <t>0.96 [0.93, 0.98]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2003,19 +2003,19 @@
         <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05800883215332904</v>
+        <v>0.05906815418722734</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003053096429122581</v>
+        <v>0.003108850220380386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009180714226198402</v>
+        <v>0.009363984211029318</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007478059043031524</v>
+        <v>0.007622146139427428</v>
       </c>
     </row>
     <row r="4">
@@ -2069,19 +2069,19 @@
         <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>1.058052363054638</v>
+        <v>1.057845862303726</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05568696647655989</v>
+        <v>0.05567609801598559</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07346164110244652</v>
+        <v>0.07332358838511423</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02027958885586174</v>
+        <v>0.02033525967511828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09109434409725803</v>
+        <v>0.0910169363568529</v>
       </c>
     </row>
     <row r="6">
@@ -2102,19 +2102,19 @@
         <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>1.398141599843694</v>
+        <v>1.397288778560707</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07358639999177335</v>
+        <v>0.07354151466108987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1191580423531833</v>
+        <v>0.1187826092116513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01615406198752757</v>
+        <v>0.01629012963875488</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1310187379960192</v>
+        <v>0.1307928996834248</v>
       </c>
     </row>
     <row r="7">
@@ -2168,19 +2168,19 @@
         <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>19.41652497158246</v>
+        <v>19.13229230228862</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9708262485791229</v>
+        <v>0.9566146151144311</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03329226488113525</v>
+        <v>0.05201130687153104</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9552449889924036</v>
+        <v>0.9322725742018273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9864075081658422</v>
+        <v>0.980956656027035</v>
       </c>
     </row>
     <row r="9">
@@ -2234,19 +2234,19 @@
         <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>0.23968618970183</v>
+        <v>0.2844350257714208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0119843094850915</v>
+        <v>0.01422175128857104</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01965816229488478</v>
+        <v>0.026281410332982</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002784006327344556</v>
+        <v>0.001921672631702127</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02118461264283845</v>
+        <v>0.02652182994543996</v>
       </c>
     </row>
     <row r="11">
@@ -2267,19 +2267,19 @@
         <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3437888387157137</v>
+        <v>0.5832726719399604</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01718944193578568</v>
+        <v>0.02916363359699802</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0217172268610419</v>
+        <v>0.0335399052433944</v>
       </c>
       <c r="H11" t="n">
-        <v>0.007025466897328424</v>
+        <v>0.01346647475313044</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02735341697424295</v>
+        <v>0.0448607924408656</v>
       </c>
     </row>
     <row r="12">
@@ -2366,16 +2366,16 @@
         <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>28.78506758122903</v>
+        <v>28.78491661504545</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9595022527076343</v>
+        <v>0.9594972205015151</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1136303358561093</v>
+        <v>0.1136285668619185</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9170719879770791</v>
+        <v>0.9170676163242466</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2399,19 +2399,19 @@
         <v>31</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8051030837922817</v>
+        <v>0.8037316472074396</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02683676945974272</v>
+        <v>0.02679105490691465</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06925665606917346</v>
+        <v>0.06923108552903291</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0009759090721682476</v>
+        <v>0.0009397427159488769</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0526976298473172</v>
+        <v>0.05264236709788043</v>
       </c>
     </row>
     <row r="16">
@@ -2432,19 +2432,19 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0284845682175833</v>
+        <v>0.03000697098600024</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009494856072527767</v>
+        <v>0.001000232366200008</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002527648112145168</v>
+        <v>0.002519977673713157</v>
       </c>
       <c r="H16" t="n">
-        <v>5.646290612745233e-06</v>
+        <v>5.925723834211423e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001893324923892808</v>
+        <v>0.001941207494057901</v>
       </c>
     </row>
     <row r="17">
@@ -2498,19 +2498,19 @@
         <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0719494670256695</v>
+        <v>0.08648443480946516</v>
       </c>
       <c r="F18" t="n">
-        <v>0.002320950549215145</v>
+        <v>0.002789820477724682</v>
       </c>
       <c r="G18" t="n">
-        <v>0.004836241923342058</v>
+        <v>0.006522226091867547</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0005470026900010572</v>
+        <v>0.0003974486327316062</v>
       </c>
       <c r="I18" t="n">
-        <v>0.004094898408429233</v>
+        <v>0.005182192322717759</v>
       </c>
     </row>
     <row r="19">
@@ -2564,19 +2564,19 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>26.92058848959772</v>
+        <v>26.91413638862177</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8684060803096038</v>
+        <v>0.868197948020057</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08984388750384137</v>
+        <v>0.08936506996716446</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8354510763153509</v>
+        <v>0.8354185757161963</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9013610843038566</v>
+        <v>0.9009773203239178</v>
       </c>
     </row>
     <row r="21">
@@ -2597,19 +2597,19 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>3.378985932357089</v>
+        <v>3.37090306554924</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1089995462050674</v>
+        <v>0.1087388085661045</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07723650935553122</v>
+        <v>0.0769433722814182</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08066896585028416</v>
+        <v>0.08051575175818301</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1373301265598506</v>
+        <v>0.136961865374026</v>
       </c>
     </row>
     <row r="22">
@@ -2663,19 +2663,19 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3102449392239586</v>
+        <v>0.2966583203223334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01000790126528899</v>
+        <v>0.009569623236204304</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01765036532339331</v>
+        <v>0.01775783383608091</v>
       </c>
       <c r="H23" t="n">
-        <v>0.003533694996024655</v>
+        <v>0.003055997198235899</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01648210753455332</v>
+        <v>0.01608324927417271</v>
       </c>
     </row>
     <row r="24">
@@ -2696,19 +2696,19 @@
         <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09974363454875398</v>
+        <v>0.1061568374238507</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003217536598346903</v>
+        <v>0.003424414110446796</v>
       </c>
       <c r="G24" t="n">
-        <v>0.003813619228905689</v>
+        <v>0.004329376783268303</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001818689771780398</v>
+        <v>0.001836385885609214</v>
       </c>
       <c r="I24" t="n">
-        <v>0.004616383424913407</v>
+        <v>0.005012442335284378</v>
       </c>
     </row>
     <row r="25">
@@ -2729,19 +2729,19 @@
         <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>3.698960904275673</v>
+        <v>3.528471066117815</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1193213194927636</v>
+        <v>0.1138216472941231</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0914289850870221</v>
+        <v>0.08629678453692791</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0857848970109952</v>
+        <v>0.08216773117229401</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1528577419745321</v>
+        <v>0.1454755634159521</v>
       </c>
     </row>
     <row r="26">
@@ -2762,19 +2762,19 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>26.7049614480441</v>
+        <v>26.88262470222849</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8614503692917451</v>
+        <v>0.8671814420073707</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1070677754544151</v>
+        <v>0.1020826396351293</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8221775921915204</v>
+        <v>0.829737227488317</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9007231463919698</v>
+        <v>0.9046256565264243</v>
       </c>
     </row>
   </sheetData>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.91 [0.89, 0.94]</t>
+          <t>0.92 [0.89, 0.94]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.77 [0.73, 0.82]</t>
+          <t>0.78 [0.73, 0.82]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.87 [0.84, 0.91]</t>
+          <t>0.88 [0.84, 0.91]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3387,19 +3387,19 @@
         <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71323124041138</v>
+        <v>16.69214999369207</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9285128466895211</v>
+        <v>0.9273416663162261</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03029159081961753</v>
+        <v>0.03136875058755241</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9134491929649404</v>
+        <v>0.9117423536410527</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9435765004141017</v>
+        <v>0.9429409789913994</v>
       </c>
     </row>
     <row r="11">
@@ -3420,19 +3420,19 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>1.269303486147326</v>
+        <v>1.290384732866636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07051686034151811</v>
+        <v>0.07168804071481312</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02966164100476489</v>
+        <v>0.03080902251371239</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05576647328990001</v>
+        <v>0.05636707426234102</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08526724739313621</v>
+        <v>0.08700900716728521</v>
       </c>
     </row>
     <row r="12">
@@ -3552,19 +3552,19 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>2.111215790220839</v>
+        <v>2.074401038577448</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1172897661233799</v>
+        <v>0.1152445021431915</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0679451680833392</v>
+        <v>0.06821958787015397</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08350142894555809</v>
+        <v>0.08131969921590258</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1510781033012017</v>
+        <v>0.1491693050704805</v>
       </c>
     </row>
     <row r="16">
@@ -3585,19 +3585,19 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>15.7268795144382</v>
+        <v>15.76369426608159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8737155285798998</v>
+        <v>0.8757607925600881</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07279049234503902</v>
+        <v>0.07329522392098764</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8375176683335739</v>
+        <v>0.8393119352060425</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9099133888262256</v>
+        <v>0.9122096499141337</v>
       </c>
     </row>
   </sheetData>
